--- a/data/trans_dic/P55$familiarvive-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P55$familiarvive-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,44</t>
+          <t>0,0; 41,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,73</t>
+          <t>0,0; 51,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,65</t>
+          <t>0,0; 36,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,9; 32,35</t>
+          <t>7,53; 33,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,95; 78,22</t>
+          <t>12,13; 79,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,03; 31,88</t>
+          <t>3,98; 31,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,65</t>
+          <t>0,0; 36,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,3; 22,27</t>
+          <t>6,17; 23,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,38; 52,81</t>
+          <t>10,54; 53,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 26,81</t>
+          <t>5,38; 27,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 31,84</t>
+          <t>2,51; 29,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,94; 23,9</t>
+          <t>9,16; 23,77</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,85</t>
+          <t>0,0; 38,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,77</t>
+          <t>0,0; 26,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,99; 55,38</t>
+          <t>6,82; 55,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 45,64</t>
+          <t>5,76; 48,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,71; 50,27</t>
+          <t>13,05; 51,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,49; 66,13</t>
+          <t>35,2; 66,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,05; 53,91</t>
+          <t>17,9; 54,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,25; 39,23</t>
+          <t>20,63; 39,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,58; 37,12</t>
+          <t>10,61; 38,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24,87; 50,17</t>
+          <t>23,55; 49,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,41; 47,81</t>
+          <t>19,01; 48,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,81; 38,07</t>
+          <t>20,34; 37,29</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,83</t>
+          <t>0,0; 37,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,79</t>
+          <t>0,0; 38,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,29</t>
+          <t>0,0; 27,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 20,11</t>
+          <t>2,52; 21,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,88; 47,89</t>
+          <t>15,76; 48,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,18; 40,84</t>
+          <t>8,2; 41,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,44; 56,25</t>
+          <t>9,29; 58,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,8; 30,59</t>
+          <t>14,26; 30,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,82; 39,41</t>
+          <t>14,77; 42,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,95; 32,16</t>
+          <t>7,95; 34,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,92; 40,19</t>
+          <t>9,0; 42,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,31; 24,45</t>
+          <t>11,59; 24,76</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,56</t>
+          <t>0,0; 34,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,32; 39,93</t>
+          <t>5,42; 41,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,3</t>
+          <t>0,0; 40,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,25</t>
+          <t>0,0; 18,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,89; 33,66</t>
+          <t>6,92; 35,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,8; 45,28</t>
+          <t>15,91; 44,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,29; 43,47</t>
+          <t>7,96; 39,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 17,84</t>
+          <t>4,56; 17,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 28,85</t>
+          <t>6,95; 29,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,73; 37,45</t>
+          <t>16,09; 38,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,57; 32,58</t>
+          <t>8,04; 32,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,5; 15,07</t>
+          <t>4,22; 14,14</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,42</t>
+          <t>0,0; 45,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1287,52 +1287,52 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,18</t>
+          <t>0,0; 83,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,96; 73,66</t>
+          <t>21,43; 71,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,2; 74,69</t>
+          <t>32,97; 71,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,95; 39,43</t>
+          <t>4,22; 37,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,6; 36,5</t>
+          <t>10,5; 33,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,65; 56,95</t>
+          <t>19,51; 57,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33,03; 65,49</t>
+          <t>31,26; 65,41</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,41; 41,81</t>
+          <t>9,08; 40,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,83; 22,56</t>
+          <t>6,8; 22,52</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,24; 37,04</t>
+          <t>5,22; 37,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,92</t>
+          <t>0,0; 22,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,24; 38,36</t>
+          <t>5,26; 38,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,68; 15,91</t>
+          <t>1,67; 15,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,09; 47,16</t>
+          <t>9,47; 47,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,09; 36,38</t>
+          <t>5,11; 40,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,14; 51,21</t>
+          <t>9,86; 51,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,52; 19,78</t>
+          <t>5,22; 18,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,78; 36,96</t>
+          <t>10,96; 36,41</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,76; 24,65</t>
+          <t>2,78; 24,57</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,0; 38,5</t>
+          <t>10,48; 38,63</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,33; 14,88</t>
+          <t>5,34; 14,71</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,22; 53,11</t>
+          <t>9,84; 51,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,69; 47,16</t>
+          <t>10,99; 47,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,81</t>
+          <t>0,0; 23,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,13</t>
+          <t>0,0; 23,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,56; 46,77</t>
+          <t>16,79; 46,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,04; 40,34</t>
+          <t>12,9; 39,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,52; 41,83</t>
+          <t>13,61; 40,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,58; 31,12</t>
+          <t>13,48; 30,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,0; 42,84</t>
+          <t>18,65; 43,08</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,08; 37,19</t>
+          <t>15,64; 37,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,8; 30,43</t>
+          <t>11,58; 31,21</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,08; 24,4</t>
+          <t>10,49; 23,56</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,09; 31,0</t>
+          <t>5,96; 31,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,89; 54,83</t>
+          <t>5,66; 55,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,07; 41,27</t>
+          <t>6,96; 38,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,65; 31,73</t>
+          <t>3,68; 31,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,74; 48,33</t>
+          <t>19,69; 48,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,55; 35,9</t>
+          <t>11,57; 35,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,58; 49,62</t>
+          <t>18,18; 48,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,06; 32,65</t>
+          <t>16,49; 32,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,24; 36,83</t>
+          <t>15,78; 36,8</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12,61; 34,27</t>
+          <t>11,47; 34,05</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19,02; 40,94</t>
+          <t>18,16; 41,42</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,45; 28,56</t>
+          <t>15,09; 28,81</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,87; 22,41</t>
+          <t>9,94; 22,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12,25; 26,09</t>
+          <t>11,84; 25,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,44; 21,32</t>
+          <t>9,96; 22,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,32; 15,23</t>
+          <t>7,05; 14,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>24,77; 37,24</t>
+          <t>24,37; 37,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,72; 35,4</t>
+          <t>23,57; 34,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,64; 33,14</t>
+          <t>20,8; 32,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16,88; 23,33</t>
+          <t>17,17; 23,44</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,76; 29,66</t>
+          <t>20,75; 30,25</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21,05; 29,7</t>
+          <t>21,27; 29,66</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18,0; 28,01</t>
+          <t>18,81; 27,81</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,38; 19,64</t>
+          <t>14,67; 19,82</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3939</t>
+          <t>0; 3639</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5976</t>
+          <t>0; 6034</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4018</t>
+          <t>0; 3319</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2134; 8747</t>
+          <t>2036; 8998</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1224; 8012</t>
+          <t>1242; 8162</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1146; 9067</t>
+          <t>1133; 9079</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 11058</t>
+          <t>0; 9010</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2072; 7327</t>
+          <t>2030; 7877</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1963; 9988</t>
+          <t>1994; 10090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2069; 10783</t>
+          <t>2164; 11159</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>821; 10748</t>
+          <t>848; 10052</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5360; 14325</t>
+          <t>5492; 14248</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5674</t>
+          <t>0; 6271</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6296</t>
+          <t>0; 6323</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>890; 7052</t>
+          <t>868; 7078</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>884; 7021</t>
+          <t>886; 7515</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2887; 11417</t>
+          <t>2964; 11710</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14601; 27997</t>
+          <t>14901; 28128</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6197; 19591</t>
+          <t>6505; 19952</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11141; 21578</t>
+          <t>11345; 21680</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4123; 14473</t>
+          <t>4136; 15010</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16380; 33037</t>
+          <t>15505; 32882</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9036; 23465</t>
+          <t>9330; 23872</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14645; 26799</t>
+          <t>14318; 26249</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3838</t>
+          <t>0; 3871</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5585</t>
+          <t>0; 5573</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4611</t>
+          <t>0; 4087</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>628; 5163</t>
+          <t>647; 5565</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6034; 17117</t>
+          <t>5634; 17255</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2167; 10818</t>
+          <t>2171; 10937</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1289; 9748</t>
+          <t>1610; 10183</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6147; 13623</t>
+          <t>6352; 13746</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6380; 18192</t>
+          <t>6820; 19398</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3249; 13151</t>
+          <t>3250; 13985</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2861; 12886</t>
+          <t>2885; 13587</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7942; 17169</t>
+          <t>8135; 17385</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4494</t>
+          <t>0; 4561</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1025; 7692</t>
+          <t>1044; 8065</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5625</t>
+          <t>0; 5602</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2855</t>
+          <t>0; 3036</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2198; 10745</t>
+          <t>2209; 11244</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6236; 17869</t>
+          <t>6280; 17373</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2435; 12771</t>
+          <t>2339; 11703</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1652; 6408</t>
+          <t>1638; 6108</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3087; 13071</t>
+          <t>3150; 13492</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8653; 21992</t>
+          <t>9448; 22396</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3283; 14120</t>
+          <t>3484; 14216</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2359; 7908</t>
+          <t>2213; 7420</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4096</t>
+          <t>0; 3919</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3051,52 +3051,52 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4102</t>
+          <t>0; 4107</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 891</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3430; 11504</t>
+          <t>3348; 11135</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8639; 18866</t>
+          <t>8329; 18118</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1195; 9527</t>
+          <t>1020; 9049</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1710; 5890</t>
+          <t>1694; 5363</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4282; 13816</t>
+          <t>4732; 14049</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11309; 22420</t>
+          <t>10704; 22395</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2446; 12163</t>
+          <t>2642; 11875</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1408; 5443</t>
+          <t>1640; 5434</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>941; 6655</t>
+          <t>938; 6709</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4145</t>
+          <t>0; 4138</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>783; 5729</t>
+          <t>786; 5747</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>406; 3848</t>
+          <t>404; 3639</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3659; 13183</t>
+          <t>2647; 13158</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1083; 7742</t>
+          <t>1088; 8694</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2372; 11977</t>
+          <t>2307; 12125</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1743; 6245</t>
+          <t>1649; 5771</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4950; 16975</t>
+          <t>5032; 16723</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1085; 9703</t>
+          <t>1095; 9671</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4214; 14754</t>
+          <t>4016; 14806</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2972; 8295</t>
+          <t>2975; 8201</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1913; 9938</t>
+          <t>1841; 9719</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3134; 13829</t>
+          <t>3223; 13928</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 6821</t>
+          <t>0; 6202</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4678</t>
+          <t>0; 5417</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6486; 18323</t>
+          <t>6576; 18157</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6439; 19914</t>
+          <t>6370; 19506</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8739; 23560</t>
+          <t>7667; 22952</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>7254; 16631</t>
+          <t>7206; 16137</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10418; 24801</t>
+          <t>10795; 24939</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12653; 29264</t>
+          <t>12308; 29152</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9764; 25184</t>
+          <t>9582; 25828</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8498; 18712</t>
+          <t>8041; 18069</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1978; 10075</t>
+          <t>1938; 10166</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1227; 11418</t>
+          <t>1179; 11546</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1748; 10208</t>
+          <t>1723; 9531</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>620; 5395</t>
+          <t>626; 5356</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8913; 22985</t>
+          <t>9363; 23153</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5418; 16835</t>
+          <t>5426; 16539</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10900; 27623</t>
+          <t>10120; 27246</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>9438; 19182</t>
+          <t>9686; 19061</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>13803; 29486</t>
+          <t>12635; 29459</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8537; 23206</t>
+          <t>7769; 23060</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>15292; 32920</t>
+          <t>14600; 33304</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>10945; 21634</t>
+          <t>11431; 21823</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>12488; 28367</t>
+          <t>12583; 28630</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>17908; 38132</t>
+          <t>17303; 37958</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11466; 25897</t>
+          <t>12101; 26920</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11495; 23915</t>
+          <t>11073; 23212</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>57205; 85990</t>
+          <t>56279; 85605</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>66306; 98944</t>
+          <t>65884; 96460</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>55186; 88615</t>
+          <t>55599; 86891</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>55413; 76583</t>
+          <t>56376; 76944</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>74219; 106044</t>
+          <t>74176; 108128</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>89589; 126445</t>
+          <t>90556; 126274</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>70004; 108901</t>
+          <t>73146; 108127</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>69807; 95337</t>
+          <t>71176; 96198</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$familiarvive-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P55$familiarvive-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,98</t>
+          <t>0,0; 45,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,23</t>
+          <t>0,0; 43,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,89</t>
+          <t>0,0; 53,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,53; 33,29</t>
+          <t>9,35; 33,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,13; 79,69</t>
+          <t>11,66; 77,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 31,93</t>
+          <t>4,01; 31,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,38</t>
+          <t>0,0; 34,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,17; 23,94</t>
+          <t>6,08; 23,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,54; 53,36</t>
+          <t>11,42; 54,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,38; 27,75</t>
+          <t>5,19; 29,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 29,77</t>
+          <t>2,39; 30,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,16; 23,77</t>
+          <t>10,38; 24,56</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,52</t>
+          <t>0,0; 38,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,88</t>
+          <t>0,0; 30,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,82; 55,59</t>
+          <t>7,67; 54,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,76; 48,85</t>
+          <t>5,62; 44,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,05; 51,57</t>
+          <t>12,32; 51,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,2; 66,44</t>
+          <t>34,95; 66,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,9; 54,9</t>
+          <t>18,33; 53,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,63; 39,42</t>
+          <t>21,39; 40,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,61; 38,5</t>
+          <t>10,0; 36,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,55; 49,93</t>
+          <t>24,89; 49,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,01; 48,64</t>
+          <t>19,01; 47,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,34; 37,29</t>
+          <t>20,23; 37,96</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,15</t>
+          <t>0,0; 37,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,71</t>
+          <t>0,0; 38,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,74</t>
+          <t>0,0; 31,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 21,67</t>
+          <t>2,44; 23,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,76; 48,27</t>
+          <t>17,71; 48,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,2; 41,28</t>
+          <t>8,1; 40,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,29; 58,77</t>
+          <t>7,24; 57,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,26; 30,87</t>
+          <t>13,75; 30,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,77; 42,02</t>
+          <t>14,52; 40,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,95; 34,2</t>
+          <t>7,67; 32,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,0; 42,37</t>
+          <t>9,73; 40,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,59; 24,76</t>
+          <t>11,37; 24,62</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,06</t>
+          <t>0,0; 34,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 41,87</t>
+          <t>5,38; 39,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,13</t>
+          <t>0,0; 39,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,35</t>
+          <t>0,0; 18,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,92; 35,22</t>
+          <t>6,95; 34,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,91; 44,02</t>
+          <t>16,22; 45,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,96; 39,83</t>
+          <t>7,62; 40,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 17,0</t>
+          <t>5,03; 18,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,95; 29,78</t>
+          <t>6,92; 29,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,09; 38,13</t>
+          <t>14,23; 37,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,04; 32,8</t>
+          <t>7,62; 32,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,22; 14,14</t>
+          <t>4,07; 14,41</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,37</t>
+          <t>0,0; 44,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,55; 75,26</t>
+          <t>11,62; 74,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,28</t>
+          <t>0,0; 66,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,42 +1297,42 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,43; 71,3</t>
+          <t>21,63; 75,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,97; 71,72</t>
+          <t>33,45; 71,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,22; 37,45</t>
+          <t>4,95; 40,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,5; 33,24</t>
+          <t>8,86; 32,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,51; 57,92</t>
+          <t>18,43; 57,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31,26; 65,41</t>
+          <t>33,09; 67,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,08; 40,82</t>
+          <t>8,17; 41,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,8; 22,52</t>
+          <t>6,03; 24,04</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,22; 37,34</t>
+          <t>5,21; 37,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,88</t>
+          <t>0,0; 28,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,26; 38,48</t>
+          <t>5,23; 38,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,67; 15,05</t>
+          <t>1,78; 15,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,47; 47,07</t>
+          <t>12,65; 47,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,11; 40,85</t>
+          <t>5,08; 35,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,86; 51,84</t>
+          <t>9,48; 50,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,22; 18,28</t>
+          <t>5,41; 19,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,96; 36,41</t>
+          <t>11,51; 38,34</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,78; 24,57</t>
+          <t>2,76; 25,46</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,48; 38,63</t>
+          <t>11,31; 40,83</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,34; 14,71</t>
+          <t>5,36; 15,22</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,84; 51,94</t>
+          <t>9,88; 54,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,99; 47,49</t>
+          <t>10,71; 49,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,47</t>
+          <t>0,0; 22,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,31</t>
+          <t>0,0; 19,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,79; 46,35</t>
+          <t>16,26; 46,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,9; 39,51</t>
+          <t>12,36; 38,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,61; 40,75</t>
+          <t>15,16; 40,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,48; 30,2</t>
+          <t>13,43; 30,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,65; 43,08</t>
+          <t>18,42; 43,81</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15,64; 37,05</t>
+          <t>15,61; 36,89</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,58; 31,21</t>
+          <t>11,55; 30,91</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,49; 23,56</t>
+          <t>11,56; 24,97</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,96; 31,28</t>
+          <t>5,99; 32,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,66; 55,44</t>
+          <t>5,46; 53,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,96; 38,53</t>
+          <t>7,05; 37,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,68; 31,5</t>
+          <t>3,45; 30,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,69; 48,68</t>
+          <t>18,3; 48,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,57; 35,27</t>
+          <t>11,76; 36,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,18; 48,94</t>
+          <t>18,2; 47,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,49; 32,44</t>
+          <t>15,85; 31,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,78; 36,8</t>
+          <t>16,83; 36,81</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11,47; 34,05</t>
+          <t>12,6; 33,89</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18,16; 41,42</t>
+          <t>17,65; 40,25</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,09; 28,81</t>
+          <t>15,3; 28,79</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,94; 22,62</t>
+          <t>9,86; 22,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,84; 25,97</t>
+          <t>12,08; 26,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,96; 22,16</t>
+          <t>9,5; 21,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,05; 14,78</t>
+          <t>7,33; 15,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>24,37; 37,07</t>
+          <t>24,39; 36,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,57; 34,51</t>
+          <t>23,66; 35,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,8; 32,5</t>
+          <t>21,34; 33,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17,17; 23,44</t>
+          <t>16,98; 23,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,75; 30,25</t>
+          <t>20,76; 30,37</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21,27; 29,66</t>
+          <t>21,13; 29,73</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18,81; 27,81</t>
+          <t>18,6; 27,77</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,67; 19,82</t>
+          <t>15,06; 20,0</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>10055</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3639</t>
+          <t>0; 3916</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6034</t>
+          <t>0; 5130</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3319</t>
+          <t>0; 4816</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2036; 8998</t>
+          <t>2734; 9933</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1242; 8162</t>
+          <t>1194; 7963</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1133; 9079</t>
+          <t>1142; 9064</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 9010</t>
+          <t>0; 8481</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2030; 7877</t>
+          <t>2041; 7736</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1994; 10090</t>
+          <t>2159; 10337</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2164; 11159</t>
+          <t>2088; 11785</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>848; 10052</t>
+          <t>808; 10322</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5492; 14248</t>
+          <t>6519; 15429</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16278</t>
+          <t>17393</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19772</t>
+          <t>21092</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6271</t>
+          <t>0; 6282</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6323</t>
+          <t>0; 7261</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>868; 7078</t>
+          <t>977; 6945</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>886; 7515</t>
+          <t>925; 7399</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2964; 11710</t>
+          <t>2799; 11716</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14901; 28128</t>
+          <t>14796; 28031</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6505; 19952</t>
+          <t>6662; 19536</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11345; 21680</t>
+          <t>12523; 23799</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4136; 15010</t>
+          <t>3899; 14184</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15505; 32882</t>
+          <t>16387; 32614</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9330; 23872</t>
+          <t>9331; 23463</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14318; 26249</t>
+          <t>15175; 28471</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2426</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9587</t>
+          <t>9711</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12013</t>
+          <t>12080</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3871</t>
+          <t>0; 3857</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5573</t>
+          <t>0; 5580</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4087</t>
+          <t>0; 4614</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>647; 5565</t>
+          <t>616; 5820</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5634; 17255</t>
+          <t>6330; 17360</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2171; 10937</t>
+          <t>2146; 10837</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1610; 10183</t>
+          <t>1255; 9980</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6352; 13746</t>
+          <t>6132; 13766</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6820; 19398</t>
+          <t>6705; 18801</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3250; 13985</t>
+          <t>3137; 13177</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2885; 13587</t>
+          <t>3120; 13027</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8135; 17385</t>
+          <t>7936; 17189</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>585</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4495</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4561</t>
+          <t>0; 4582</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1044; 8065</t>
+          <t>1037; 7657</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5602</t>
+          <t>0; 5582</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3036</t>
+          <t>0; 3328</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2209; 11244</t>
+          <t>2220; 11097</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6280; 17373</t>
+          <t>6402; 18034</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2339; 11703</t>
+          <t>2238; 11886</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1638; 6108</t>
+          <t>1911; 7102</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3150; 13492</t>
+          <t>3137; 13437</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9448; 22396</t>
+          <t>8355; 22114</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3484; 14216</t>
+          <t>3301; 14210</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2213; 7420</t>
+          <t>2267; 8034</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>3258</t>
         </is>
       </c>
     </row>
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3919</t>
+          <t>0; 3852</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1037; 6754</t>
+          <t>1043; 6724</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4107</t>
+          <t>0; 3298</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3061,42 +3061,42 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3348; 11135</t>
+          <t>3378; 11720</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8329; 18118</t>
+          <t>8449; 17956</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1020; 9049</t>
+          <t>1196; 9895</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1694; 5363</t>
+          <t>1488; 5539</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4732; 14049</t>
+          <t>4471; 13868</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10704; 22395</t>
+          <t>11328; 23163</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2642; 11875</t>
+          <t>2376; 11999</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1640; 5434</t>
+          <t>1508; 6010</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>1682</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>5151</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>938; 6709</t>
+          <t>936; 6684</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4138</t>
+          <t>0; 5176</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>786; 5747</t>
+          <t>782; 5702</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>404; 3639</t>
+          <t>432; 3799</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2647; 13158</t>
+          <t>3537; 13293</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1088; 8694</t>
+          <t>1081; 7644</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2307; 12125</t>
+          <t>2217; 11710</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1649; 5771</t>
+          <t>1740; 6206</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5032; 16723</t>
+          <t>5285; 17608</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1095; 9671</t>
+          <t>1088; 10023</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4016; 14806</t>
+          <t>4333; 15647</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2975; 8201</t>
+          <t>3021; 8579</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>11264</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>12746</t>
+          <t>15840</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1841; 9719</t>
+          <t>1849; 10176</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3223; 13928</t>
+          <t>3142; 14378</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 6202</t>
+          <t>0; 5917</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 5417</t>
+          <t>0; 5557</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6576; 18157</t>
+          <t>6369; 18221</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6370; 19506</t>
+          <t>6100; 18887</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7667; 22952</t>
+          <t>8540; 22940</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>7206; 16137</t>
+          <t>8763; 19887</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10795; 24939</t>
+          <t>10661; 25359</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12308; 29152</t>
+          <t>12281; 29030</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9582; 25828</t>
+          <t>9560; 25582</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8041; 18069</t>
+          <t>10852; 23436</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>13839</t>
+          <t>15763</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>16284</t>
+          <t>18431</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1938; 10166</t>
+          <t>1945; 10574</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1179; 11546</t>
+          <t>1137; 11093</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1723; 9531</t>
+          <t>1744; 9303</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>626; 5356</t>
+          <t>670; 5982</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9363; 23153</t>
+          <t>8703; 22857</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5426; 16539</t>
+          <t>5512; 17058</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10120; 27246</t>
+          <t>10130; 26274</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>9686; 19061</t>
+          <t>10826; 21758</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>12635; 29459</t>
+          <t>13472; 29466</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>7769; 23060</t>
+          <t>8535; 22951</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>14600; 33304</t>
+          <t>14195; 32361</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>11431; 21823</t>
+          <t>13423; 25257</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16980</t>
+          <t>18484</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>65663</t>
+          <t>71918</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>82643</t>
+          <t>90402</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>12583; 28630</t>
+          <t>12479; 28676</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>17303; 37958</t>
+          <t>17651; 38661</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12101; 26920</t>
+          <t>11535; 26314</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11073; 23212</t>
+          <t>12401; 25873</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>56279; 85605</t>
+          <t>56317; 84259</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>65884; 96460</t>
+          <t>66146; 98151</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>55599; 86891</t>
+          <t>57053; 88563</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>56376; 76944</t>
+          <t>60645; 84124</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>74176; 108128</t>
+          <t>74223; 108590</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>90556; 126274</t>
+          <t>89947; 126573</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>73146; 108127</t>
+          <t>72307; 107990</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>71176; 96198</t>
+          <t>79288; 105282</t>
         </is>
       </c>
     </row>
